--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1413,6 +1413,1355 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121509872</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5172</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norrn, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>705878</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6645330</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121510395</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57370</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norrn, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>705903</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6645116</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121510211</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57370</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norrn, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>705870</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6645222</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121510617</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105203</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norrn, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>705913</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6645098</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121510346</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57370</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norrn, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>705926</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6645152</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121511629</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100364</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norrn, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>705996</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6645057</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121510018</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90678</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norrn, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>705808</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6645334</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121511055</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57370</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norrn, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>705844</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6645172</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121510646</v>
+      </c>
+      <c r="B16" t="n">
+        <v>105203</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norrn, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>705903</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6645116</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121512264</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97052</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norrn, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>705936</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6645491</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121510232</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90678</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norrn, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>705933</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6645178</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121510250</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100364</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norrn, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>705934</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6645213</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121510391</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100364</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norrn, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>705926</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6645152</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121509872</v>
+        <v>121512264</v>
       </c>
       <c r="B8" t="n">
-        <v>5172</v>
+        <v>97058</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705878</v>
+        <v>705936</v>
       </c>
       <c r="R8" t="n">
-        <v>6645330</v>
+        <v>6645491</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121510395</v>
+        <v>121510646</v>
       </c>
       <c r="B9" t="n">
-        <v>57370</v>
+        <v>105209</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,33 +1529,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
@@ -1624,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121510211</v>
+        <v>121510391</v>
       </c>
       <c r="B10" t="n">
-        <v>57370</v>
+        <v>100370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,43 +1631,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705870</v>
+        <v>705926</v>
       </c>
       <c r="R10" t="n">
-        <v>6645222</v>
+        <v>6645152</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1731,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121510617</v>
+        <v>121509872</v>
       </c>
       <c r="B11" t="n">
-        <v>105203</v>
+        <v>5172</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,21 +1737,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>705913</v>
+        <v>705878</v>
       </c>
       <c r="R11" t="n">
-        <v>6645098</v>
+        <v>6645330</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121510346</v>
+        <v>121510395</v>
       </c>
       <c r="B12" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,13 +1868,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705926</v>
+        <v>705903</v>
       </c>
       <c r="R12" t="n">
-        <v>6645152</v>
+        <v>6645116</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1940,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121511629</v>
+        <v>121510617</v>
       </c>
       <c r="B13" t="n">
-        <v>100364</v>
+        <v>105209</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1946,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1980,13 +1970,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705996</v>
+        <v>705913</v>
       </c>
       <c r="R13" t="n">
-        <v>6645057</v>
+        <v>6645098</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2045,7 +2035,7 @@
         <v>121510018</v>
       </c>
       <c r="B14" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2144,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121511055</v>
+        <v>121511629</v>
       </c>
       <c r="B15" t="n">
-        <v>57370</v>
+        <v>100370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,49 +2146,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705844</v>
+        <v>705996</v>
       </c>
       <c r="R15" t="n">
-        <v>6645172</v>
+        <v>6645057</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2254,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121510646</v>
+        <v>121510250</v>
       </c>
       <c r="B16" t="n">
-        <v>105203</v>
+        <v>100370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2270,21 +2252,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2294,10 +2276,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705903</v>
+        <v>705934</v>
       </c>
       <c r="R16" t="n">
-        <v>6645116</v>
+        <v>6645213</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121512264</v>
+        <v>121510346</v>
       </c>
       <c r="B17" t="n">
-        <v>97052</v>
+        <v>57371</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2368,41 +2350,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705936</v>
+        <v>705926</v>
       </c>
       <c r="R17" t="n">
-        <v>6645491</v>
+        <v>6645152</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2458,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121510232</v>
+        <v>121511055</v>
       </c>
       <c r="B18" t="n">
-        <v>90678</v>
+        <v>57371</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,41 +2457,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705933</v>
+        <v>705844</v>
       </c>
       <c r="R18" t="n">
-        <v>6645178</v>
+        <v>6645172</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2560,10 +2555,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121510250</v>
+        <v>121510232</v>
       </c>
       <c r="B19" t="n">
-        <v>100364</v>
+        <v>90684</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2571,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2595,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>705934</v>
+        <v>705933</v>
       </c>
       <c r="R19" t="n">
-        <v>6645213</v>
+        <v>6645178</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2662,10 +2657,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121510391</v>
+        <v>121510211</v>
       </c>
       <c r="B20" t="n">
-        <v>100364</v>
+        <v>57371</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2674,38 +2669,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>705926</v>
+        <v>705870</v>
       </c>
       <c r="R20" t="n">
-        <v>6645152</v>
+        <v>6645222</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121512264</v>
+        <v>121510018</v>
       </c>
       <c r="B8" t="n">
-        <v>97058</v>
+        <v>90685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705936</v>
+        <v>705808</v>
       </c>
       <c r="R8" t="n">
-        <v>6645491</v>
+        <v>6645334</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121510646</v>
+        <v>121511629</v>
       </c>
       <c r="B9" t="n">
-        <v>105209</v>
+        <v>100371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,21 +1533,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>705903</v>
+        <v>705996</v>
       </c>
       <c r="R9" t="n">
-        <v>6645116</v>
+        <v>6645057</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121510391</v>
+        <v>121510250</v>
       </c>
       <c r="B10" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705926</v>
+        <v>705934</v>
       </c>
       <c r="R10" t="n">
-        <v>6645152</v>
+        <v>6645213</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121509872</v>
+        <v>121510232</v>
       </c>
       <c r="B11" t="n">
-        <v>5172</v>
+        <v>90685</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,21 +1737,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>705878</v>
+        <v>705933</v>
       </c>
       <c r="R11" t="n">
-        <v>6645330</v>
+        <v>6645178</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,7 +1826,7 @@
         <v>121510395</v>
       </c>
       <c r="B12" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>121510617</v>
       </c>
       <c r="B13" t="n">
-        <v>105209</v>
+        <v>105210</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121510018</v>
+        <v>121510646</v>
       </c>
       <c r="B14" t="n">
-        <v>90684</v>
+        <v>105210</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,21 +2048,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705808</v>
+        <v>705903</v>
       </c>
       <c r="R14" t="n">
-        <v>6645334</v>
+        <v>6645116</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2134,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121511629</v>
+        <v>121510391</v>
       </c>
       <c r="B15" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705996</v>
+        <v>705926</v>
       </c>
       <c r="R15" t="n">
-        <v>6645057</v>
+        <v>6645152</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121510250</v>
+        <v>121510346</v>
       </c>
       <c r="B16" t="n">
-        <v>100370</v>
+        <v>57372</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2248,41 +2248,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705934</v>
+        <v>705926</v>
       </c>
       <c r="R16" t="n">
-        <v>6645213</v>
+        <v>6645152</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2338,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121510346</v>
+        <v>121509872</v>
       </c>
       <c r="B17" t="n">
-        <v>57371</v>
+        <v>5172</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2350,46 +2355,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705926</v>
+        <v>705878</v>
       </c>
       <c r="R17" t="n">
-        <v>6645152</v>
+        <v>6645330</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121511055</v>
+        <v>121512264</v>
       </c>
       <c r="B18" t="n">
-        <v>57371</v>
+        <v>97059</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2457,49 +2457,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705844</v>
+        <v>705936</v>
       </c>
       <c r="R18" t="n">
-        <v>6645172</v>
+        <v>6645491</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,10 +2547,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121510232</v>
+        <v>121511055</v>
       </c>
       <c r="B19" t="n">
-        <v>90684</v>
+        <v>57372</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2567,41 +2559,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>705933</v>
+        <v>705844</v>
       </c>
       <c r="R19" t="n">
-        <v>6645178</v>
+        <v>6645172</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>121510211</v>
       </c>
       <c r="B20" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121510018</v>
+        <v>121510391</v>
       </c>
       <c r="B8" t="n">
-        <v>90685</v>
+        <v>100371</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705808</v>
+        <v>705926</v>
       </c>
       <c r="R8" t="n">
-        <v>6645334</v>
+        <v>6645152</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121511629</v>
+        <v>121511055</v>
       </c>
       <c r="B9" t="n">
-        <v>100371</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,41 +1529,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>705996</v>
+        <v>705844</v>
       </c>
       <c r="R9" t="n">
-        <v>6645057</v>
+        <v>6645172</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,10 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121510250</v>
+        <v>121510018</v>
       </c>
       <c r="B10" t="n">
-        <v>100371</v>
+        <v>90685</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,21 +1643,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,13 +1667,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705934</v>
+        <v>705808</v>
       </c>
       <c r="R10" t="n">
-        <v>6645213</v>
+        <v>6645334</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1930,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121510617</v>
+        <v>121510211</v>
       </c>
       <c r="B13" t="n">
-        <v>105210</v>
+        <v>57372</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,41 +1950,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705913</v>
+        <v>705870</v>
       </c>
       <c r="R13" t="n">
-        <v>6645098</v>
+        <v>6645222</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2032,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121510646</v>
+        <v>121510250</v>
       </c>
       <c r="B14" t="n">
-        <v>105210</v>
+        <v>100371</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,21 +2061,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705903</v>
+        <v>705934</v>
       </c>
       <c r="R14" t="n">
-        <v>6645116</v>
+        <v>6645213</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,10 +2147,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121510391</v>
+        <v>121510646</v>
       </c>
       <c r="B15" t="n">
-        <v>100371</v>
+        <v>105210</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2150,21 +2163,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2174,13 +2187,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705926</v>
+        <v>705903</v>
       </c>
       <c r="R15" t="n">
-        <v>6645152</v>
+        <v>6645116</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2236,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121510346</v>
+        <v>121509872</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2248,46 +2261,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705926</v>
+        <v>705878</v>
       </c>
       <c r="R16" t="n">
-        <v>6645152</v>
+        <v>6645330</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2343,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121509872</v>
+        <v>121511629</v>
       </c>
       <c r="B17" t="n">
-        <v>5172</v>
+        <v>100371</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2359,21 +2367,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2383,13 +2391,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705878</v>
+        <v>705996</v>
       </c>
       <c r="R17" t="n">
-        <v>6645330</v>
+        <v>6645057</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2445,10 +2453,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121512264</v>
+        <v>121510617</v>
       </c>
       <c r="B18" t="n">
-        <v>97059</v>
+        <v>105210</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2461,21 +2469,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2485,10 +2493,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705936</v>
+        <v>705913</v>
       </c>
       <c r="R18" t="n">
-        <v>6645491</v>
+        <v>6645098</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,10 +2555,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121511055</v>
+        <v>121512264</v>
       </c>
       <c r="B19" t="n">
-        <v>57372</v>
+        <v>97059</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2559,49 +2567,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>705844</v>
+        <v>705936</v>
       </c>
       <c r="R19" t="n">
-        <v>6645172</v>
+        <v>6645491</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121510211</v>
+        <v>121510346</v>
       </c>
       <c r="B20" t="n">
         <v>57372</v>
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>705870</v>
+        <v>705926</v>
       </c>
       <c r="R20" t="n">
-        <v>6645222</v>
+        <v>6645152</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121510391</v>
+        <v>121509872</v>
       </c>
       <c r="B8" t="n">
-        <v>100371</v>
+        <v>5172</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705926</v>
+        <v>705878</v>
       </c>
       <c r="R8" t="n">
-        <v>6645152</v>
+        <v>6645330</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121511055</v>
+        <v>121510250</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>100371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,49 +1529,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>705844</v>
+        <v>705934</v>
       </c>
       <c r="R9" t="n">
-        <v>6645172</v>
+        <v>6645213</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1627,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121510018</v>
+        <v>121510646</v>
       </c>
       <c r="B10" t="n">
-        <v>90685</v>
+        <v>105210</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1643,21 +1635,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,13 +1659,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705808</v>
+        <v>705903</v>
       </c>
       <c r="R10" t="n">
-        <v>6645334</v>
+        <v>6645116</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1729,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121510232</v>
+        <v>121510211</v>
       </c>
       <c r="B11" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,41 +1733,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>705933</v>
+        <v>705870</v>
       </c>
       <c r="R11" t="n">
-        <v>6645178</v>
+        <v>6645222</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1831,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121510395</v>
+        <v>121510018</v>
       </c>
       <c r="B12" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,46 +1840,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705903</v>
+        <v>705808</v>
       </c>
       <c r="R12" t="n">
-        <v>6645116</v>
+        <v>6645334</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,7 +1930,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121510211</v>
+        <v>121510346</v>
       </c>
       <c r="B13" t="n">
         <v>57372</v>
@@ -1983,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705870</v>
+        <v>705926</v>
       </c>
       <c r="R13" t="n">
-        <v>6645222</v>
+        <v>6645152</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2045,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121510250</v>
+        <v>121510395</v>
       </c>
       <c r="B14" t="n">
-        <v>100371</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,38 +2049,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705934</v>
+        <v>705903</v>
       </c>
       <c r="R14" t="n">
-        <v>6645213</v>
+        <v>6645116</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2147,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121510646</v>
+        <v>121511629</v>
       </c>
       <c r="B15" t="n">
-        <v>105210</v>
+        <v>100371</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2163,21 +2160,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2187,13 +2184,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705903</v>
+        <v>705996</v>
       </c>
       <c r="R15" t="n">
-        <v>6645116</v>
+        <v>6645057</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2249,10 +2246,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121509872</v>
+        <v>121510232</v>
       </c>
       <c r="B16" t="n">
-        <v>5172</v>
+        <v>90685</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2265,21 +2262,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2289,10 +2286,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705878</v>
+        <v>705933</v>
       </c>
       <c r="R16" t="n">
-        <v>6645330</v>
+        <v>6645178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,7 +2348,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121511629</v>
+        <v>121510391</v>
       </c>
       <c r="B17" t="n">
         <v>100371</v>
@@ -2391,10 +2388,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705996</v>
+        <v>705926</v>
       </c>
       <c r="R17" t="n">
-        <v>6645057</v>
+        <v>6645152</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2453,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121510617</v>
+        <v>121511055</v>
       </c>
       <c r="B18" t="n">
-        <v>105210</v>
+        <v>57372</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2465,41 +2462,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705913</v>
+        <v>705844</v>
       </c>
       <c r="R18" t="n">
-        <v>6645098</v>
+        <v>6645172</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121512264</v>
+        <v>121510617</v>
       </c>
       <c r="B19" t="n">
-        <v>97059</v>
+        <v>105210</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2571,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2595,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>705936</v>
+        <v>705913</v>
       </c>
       <c r="R19" t="n">
-        <v>6645491</v>
+        <v>6645098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2657,10 +2662,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121510346</v>
+        <v>121512264</v>
       </c>
       <c r="B20" t="n">
-        <v>57372</v>
+        <v>97059</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2669,46 +2674,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>705926</v>
+        <v>705936</v>
       </c>
       <c r="R20" t="n">
-        <v>6645152</v>
+        <v>6645491</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121509872</v>
+        <v>121512264</v>
       </c>
       <c r="B8" t="n">
-        <v>5172</v>
+        <v>97059</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705878</v>
+        <v>705936</v>
       </c>
       <c r="R8" t="n">
-        <v>6645330</v>
+        <v>6645491</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121510646</v>
+        <v>121510391</v>
       </c>
       <c r="B10" t="n">
-        <v>105210</v>
+        <v>100371</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,21 +1635,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705903</v>
+        <v>705926</v>
       </c>
       <c r="R10" t="n">
-        <v>6645116</v>
+        <v>6645152</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121510211</v>
+        <v>121509872</v>
       </c>
       <c r="B11" t="n">
-        <v>57372</v>
+        <v>5172</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,46 +1733,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>705870</v>
+        <v>705878</v>
       </c>
       <c r="R11" t="n">
-        <v>6645222</v>
+        <v>6645330</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1828,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121510018</v>
+        <v>121510395</v>
       </c>
       <c r="B12" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,41 +1835,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705808</v>
+        <v>705903</v>
       </c>
       <c r="R12" t="n">
-        <v>6645334</v>
+        <v>6645116</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121510346</v>
+        <v>121510232</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,46 +1942,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705926</v>
+        <v>705933</v>
       </c>
       <c r="R13" t="n">
-        <v>6645152</v>
+        <v>6645178</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2037,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121510395</v>
+        <v>121510617</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>105210</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,43 +2044,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705903</v>
+        <v>705913</v>
       </c>
       <c r="R14" t="n">
-        <v>6645116</v>
+        <v>6645098</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2144,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121511629</v>
+        <v>121510211</v>
       </c>
       <c r="B15" t="n">
-        <v>100371</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,38 +2146,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705996</v>
+        <v>705870</v>
       </c>
       <c r="R15" t="n">
-        <v>6645057</v>
+        <v>6645222</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2246,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121510232</v>
+        <v>121510346</v>
       </c>
       <c r="B16" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2258,41 +2253,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705933</v>
+        <v>705926</v>
       </c>
       <c r="R16" t="n">
-        <v>6645178</v>
+        <v>6645152</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121510391</v>
+        <v>121511055</v>
       </c>
       <c r="B17" t="n">
-        <v>100371</v>
+        <v>57372</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2360,41 +2360,49 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705926</v>
+        <v>705844</v>
       </c>
       <c r="R17" t="n">
-        <v>6645152</v>
+        <v>6645172</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2450,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121511055</v>
+        <v>121510018</v>
       </c>
       <c r="B18" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2462,49 +2470,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705844</v>
+        <v>705808</v>
       </c>
       <c r="R18" t="n">
-        <v>6645172</v>
+        <v>6645334</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121510617</v>
+        <v>121511629</v>
       </c>
       <c r="B19" t="n">
-        <v>105210</v>
+        <v>100371</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,13 +2600,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>705913</v>
+        <v>705996</v>
       </c>
       <c r="R19" t="n">
-        <v>6645098</v>
+        <v>6645057</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121512264</v>
+        <v>121510646</v>
       </c>
       <c r="B20" t="n">
-        <v>97059</v>
+        <v>105210</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2678,21 +2678,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>705936</v>
+        <v>705903</v>
       </c>
       <c r="R20" t="n">
-        <v>6645491</v>
+        <v>6645116</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121510250</v>
+        <v>121509872</v>
       </c>
       <c r="B9" t="n">
-        <v>100371</v>
+        <v>5172</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,21 +1533,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>705934</v>
+        <v>705878</v>
       </c>
       <c r="R9" t="n">
-        <v>6645213</v>
+        <v>6645330</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121510391</v>
+        <v>121510250</v>
       </c>
       <c r="B10" t="n">
         <v>100371</v>
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705926</v>
+        <v>705934</v>
       </c>
       <c r="R10" t="n">
-        <v>6645152</v>
+        <v>6645213</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121509872</v>
+        <v>121510391</v>
       </c>
       <c r="B11" t="n">
-        <v>5172</v>
+        <v>100371</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,21 +1737,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>705878</v>
+        <v>705926</v>
       </c>
       <c r="R11" t="n">
-        <v>6645330</v>
+        <v>6645152</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -1418,7 +1418,7 @@
         <v>121512264</v>
       </c>
       <c r="B8" t="n">
-        <v>97059</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121509872</v>
+        <v>121510395</v>
       </c>
       <c r="B9" t="n">
-        <v>5172</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,38 +1529,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>705878</v>
+        <v>705903</v>
       </c>
       <c r="R9" t="n">
-        <v>6645330</v>
+        <v>6645116</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1619,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121510250</v>
+        <v>121510211</v>
       </c>
       <c r="B10" t="n">
-        <v>100371</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,41 +1636,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705934</v>
+        <v>705870</v>
       </c>
       <c r="R10" t="n">
-        <v>6645213</v>
+        <v>6645222</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1721,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121510391</v>
+        <v>121511055</v>
       </c>
       <c r="B11" t="n">
-        <v>100371</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,41 +1743,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>705926</v>
+        <v>705844</v>
       </c>
       <c r="R11" t="n">
-        <v>6645152</v>
+        <v>6645172</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1823,10 +1841,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121510395</v>
+        <v>121510232</v>
       </c>
       <c r="B12" t="n">
-        <v>57372</v>
+        <v>90693</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,43 +1853,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705903</v>
+        <v>705933</v>
       </c>
       <c r="R12" t="n">
-        <v>6645116</v>
+        <v>6645178</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121510232</v>
+        <v>121510250</v>
       </c>
       <c r="B13" t="n">
-        <v>90685</v>
+        <v>100379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,21 +1959,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1970,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705933</v>
+        <v>705934</v>
       </c>
       <c r="R13" t="n">
-        <v>6645178</v>
+        <v>6645213</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121510617</v>
+        <v>121510391</v>
       </c>
       <c r="B14" t="n">
-        <v>105210</v>
+        <v>100379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,21 +2061,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,13 +2085,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705913</v>
+        <v>705926</v>
       </c>
       <c r="R14" t="n">
-        <v>6645098</v>
+        <v>6645152</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2134,10 +2147,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121510211</v>
+        <v>121510346</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,10 +2192,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705870</v>
+        <v>705926</v>
       </c>
       <c r="R15" t="n">
-        <v>6645222</v>
+        <v>6645152</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2241,10 +2254,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121510346</v>
+        <v>121511629</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>100379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,43 +2266,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705926</v>
+        <v>705996</v>
       </c>
       <c r="R16" t="n">
-        <v>6645152</v>
+        <v>6645057</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2348,10 +2356,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121511055</v>
+        <v>121510018</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>90693</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2360,49 +2368,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705844</v>
+        <v>705808</v>
       </c>
       <c r="R17" t="n">
-        <v>6645172</v>
+        <v>6645334</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2458,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121510018</v>
+        <v>121510617</v>
       </c>
       <c r="B18" t="n">
-        <v>90685</v>
+        <v>105218</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2474,21 +2474,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705808</v>
+        <v>705913</v>
       </c>
       <c r="R18" t="n">
-        <v>6645334</v>
+        <v>6645098</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121511629</v>
+        <v>121509872</v>
       </c>
       <c r="B19" t="n">
-        <v>100371</v>
+        <v>5173</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,13 +2600,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>705996</v>
+        <v>705878</v>
       </c>
       <c r="R19" t="n">
-        <v>6645057</v>
+        <v>6645330</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>121510646</v>
       </c>
       <c r="B20" t="n">
-        <v>105210</v>
+        <v>105218</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121510211</v>
+        <v>121510232</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>90693</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,46 +1427,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705870</v>
+        <v>705933</v>
       </c>
       <c r="R8" t="n">
-        <v>6645222</v>
+        <v>6645178</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1522,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121510250</v>
+        <v>121510346</v>
       </c>
       <c r="B9" t="n">
-        <v>100379</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,41 +1529,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>705934</v>
+        <v>705926</v>
       </c>
       <c r="R9" t="n">
-        <v>6645213</v>
+        <v>6645152</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121510391</v>
+        <v>121510211</v>
       </c>
       <c r="B10" t="n">
-        <v>100379</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,38 +1636,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705926</v>
+        <v>705870</v>
       </c>
       <c r="R10" t="n">
-        <v>6645152</v>
+        <v>6645222</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1726,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121509872</v>
+        <v>121511629</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>100379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,21 +1747,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1766,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>705878</v>
+        <v>705996</v>
       </c>
       <c r="R11" t="n">
-        <v>6645330</v>
+        <v>6645057</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1828,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121510395</v>
+        <v>121510646</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,33 +1845,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121510646</v>
+        <v>121509872</v>
       </c>
       <c r="B13" t="n">
-        <v>105218</v>
+        <v>5173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,21 +1951,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705903</v>
+        <v>705878</v>
       </c>
       <c r="R13" t="n">
-        <v>6645116</v>
+        <v>6645330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121511055</v>
+        <v>121510391</v>
       </c>
       <c r="B14" t="n">
-        <v>57373</v>
+        <v>100379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,49 +2049,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705844</v>
+        <v>705926</v>
       </c>
       <c r="R14" t="n">
-        <v>6645172</v>
+        <v>6645152</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2147,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121510346</v>
+        <v>121512264</v>
       </c>
       <c r="B15" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,46 +2151,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705926</v>
+        <v>705936</v>
       </c>
       <c r="R15" t="n">
-        <v>6645152</v>
+        <v>6645491</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2254,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121512264</v>
+        <v>121510250</v>
       </c>
       <c r="B16" t="n">
-        <v>97067</v>
+        <v>100379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2270,21 +2257,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2294,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705936</v>
+        <v>705934</v>
       </c>
       <c r="R16" t="n">
-        <v>6645491</v>
+        <v>6645213</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121511629</v>
+        <v>121510617</v>
       </c>
       <c r="B17" t="n">
-        <v>100379</v>
+        <v>105218</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2372,21 +2359,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,13 +2383,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705996</v>
+        <v>705913</v>
       </c>
       <c r="R17" t="n">
-        <v>6645057</v>
+        <v>6645098</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2458,10 +2445,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121510018</v>
+        <v>121510395</v>
       </c>
       <c r="B18" t="n">
-        <v>90693</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,41 +2457,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705808</v>
+        <v>705903</v>
       </c>
       <c r="R18" t="n">
-        <v>6645334</v>
+        <v>6645116</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2560,7 +2552,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121510232</v>
+        <v>121510018</v>
       </c>
       <c r="B19" t="n">
         <v>90693</v>
@@ -2600,13 +2592,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>705933</v>
+        <v>705808</v>
       </c>
       <c r="R19" t="n">
-        <v>6645178</v>
+        <v>6645334</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2662,10 +2654,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121510617</v>
+        <v>121511055</v>
       </c>
       <c r="B20" t="n">
-        <v>105218</v>
+        <v>57373</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2674,41 +2666,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>705913</v>
+        <v>705844</v>
       </c>
       <c r="R20" t="n">
-        <v>6645098</v>
+        <v>6645172</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -2241,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121510250</v>
+        <v>121510617</v>
       </c>
       <c r="B16" t="n">
-        <v>100379</v>
+        <v>105218</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705934</v>
+        <v>705913</v>
       </c>
       <c r="R16" t="n">
-        <v>6645213</v>
+        <v>6645098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121510617</v>
+        <v>121510250</v>
       </c>
       <c r="B17" t="n">
-        <v>105218</v>
+        <v>100379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2359,21 +2359,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705913</v>
+        <v>705934</v>
       </c>
       <c r="R17" t="n">
-        <v>6645098</v>
+        <v>6645213</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -1415,7 +1415,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121510232</v>
+        <v>121510018</v>
       </c>
       <c r="B8" t="n">
         <v>90693</v>
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705933</v>
+        <v>705808</v>
       </c>
       <c r="R8" t="n">
-        <v>6645178</v>
+        <v>6645334</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121510346</v>
+        <v>121510391</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>100379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,33 +1529,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
@@ -1624,7 +1619,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121510211</v>
+        <v>121511055</v>
       </c>
       <c r="B10" t="n">
         <v>57373</v>
@@ -1658,24 +1653,27 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705870</v>
+        <v>705844</v>
       </c>
       <c r="R10" t="n">
-        <v>6645222</v>
+        <v>6645172</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1731,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121511629</v>
+        <v>121510617</v>
       </c>
       <c r="B11" t="n">
-        <v>100379</v>
+        <v>105218</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,21 +1745,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,13 +1769,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>705996</v>
+        <v>705913</v>
       </c>
       <c r="R11" t="n">
-        <v>6645057</v>
+        <v>6645098</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1833,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121510646</v>
+        <v>121510346</v>
       </c>
       <c r="B12" t="n">
-        <v>105218</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,41 +1843,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705903</v>
+        <v>705926</v>
       </c>
       <c r="R12" t="n">
-        <v>6645116</v>
+        <v>6645152</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1935,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121509872</v>
+        <v>121510646</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
+        <v>105218</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,21 +1954,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1975,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705878</v>
+        <v>705903</v>
       </c>
       <c r="R13" t="n">
-        <v>6645330</v>
+        <v>6645116</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121510391</v>
+        <v>121512264</v>
       </c>
       <c r="B14" t="n">
-        <v>100379</v>
+        <v>97067</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,21 +2056,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2077,13 +2080,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705926</v>
+        <v>705936</v>
       </c>
       <c r="R14" t="n">
-        <v>6645152</v>
+        <v>6645491</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2139,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121512264</v>
+        <v>121511629</v>
       </c>
       <c r="B15" t="n">
-        <v>97067</v>
+        <v>100379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,21 +2158,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,13 +2182,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705936</v>
+        <v>705996</v>
       </c>
       <c r="R15" t="n">
-        <v>6645491</v>
+        <v>6645057</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2241,10 +2244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121510617</v>
+        <v>121510250</v>
       </c>
       <c r="B16" t="n">
-        <v>105218</v>
+        <v>100379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2257,21 +2260,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2281,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705913</v>
+        <v>705934</v>
       </c>
       <c r="R16" t="n">
-        <v>6645098</v>
+        <v>6645213</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121510250</v>
+        <v>121510232</v>
       </c>
       <c r="B17" t="n">
-        <v>100379</v>
+        <v>90693</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2359,21 +2362,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2383,10 +2386,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705934</v>
+        <v>705933</v>
       </c>
       <c r="R17" t="n">
-        <v>6645213</v>
+        <v>6645178</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2445,7 +2448,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121510395</v>
+        <v>121510211</v>
       </c>
       <c r="B18" t="n">
         <v>57373</v>
@@ -2490,13 +2493,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705903</v>
+        <v>705870</v>
       </c>
       <c r="R18" t="n">
-        <v>6645116</v>
+        <v>6645222</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2552,10 +2555,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121510018</v>
+        <v>121510395</v>
       </c>
       <c r="B19" t="n">
-        <v>90693</v>
+        <v>57373</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2564,41 +2567,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>705808</v>
+        <v>705903</v>
       </c>
       <c r="R19" t="n">
-        <v>6645334</v>
+        <v>6645116</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2654,10 +2662,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121511055</v>
+        <v>121509872</v>
       </c>
       <c r="B20" t="n">
-        <v>57373</v>
+        <v>5173</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2666,49 +2674,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>705844</v>
+        <v>705878</v>
       </c>
       <c r="R20" t="n">
-        <v>6645172</v>
+        <v>6645330</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -1729,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121510617</v>
+        <v>121510346</v>
       </c>
       <c r="B11" t="n">
-        <v>105218</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,41 +1741,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>705913</v>
+        <v>705926</v>
       </c>
       <c r="R11" t="n">
-        <v>6645098</v>
+        <v>6645152</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1831,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121510346</v>
+        <v>121510617</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,46 +1848,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705926</v>
+        <v>705913</v>
       </c>
       <c r="R12" t="n">
-        <v>6645152</v>
+        <v>6645098</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121510646</v>
+        <v>121512264</v>
       </c>
       <c r="B13" t="n">
-        <v>105218</v>
+        <v>97067</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,21 +1954,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705903</v>
+        <v>705936</v>
       </c>
       <c r="R13" t="n">
-        <v>6645116</v>
+        <v>6645491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121512264</v>
+        <v>121510646</v>
       </c>
       <c r="B14" t="n">
-        <v>97067</v>
+        <v>105218</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705936</v>
+        <v>705903</v>
       </c>
       <c r="R14" t="n">
-        <v>6645491</v>
+        <v>6645116</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121510018</v>
+        <v>121511055</v>
       </c>
       <c r="B8" t="n">
-        <v>90693</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,41 +1427,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705808</v>
+        <v>705844</v>
       </c>
       <c r="R8" t="n">
-        <v>6645334</v>
+        <v>6645172</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1517,10 +1525,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121510391</v>
+        <v>121510617</v>
       </c>
       <c r="B9" t="n">
-        <v>100379</v>
+        <v>105218</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,21 +1541,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,13 +1565,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>705926</v>
+        <v>705913</v>
       </c>
       <c r="R9" t="n">
-        <v>6645152</v>
+        <v>6645098</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,7 +1627,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121511055</v>
+        <v>121510211</v>
       </c>
       <c r="B10" t="n">
         <v>57373</v>
@@ -1653,27 +1661,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705844</v>
+        <v>705870</v>
       </c>
       <c r="R10" t="n">
-        <v>6645172</v>
+        <v>6645222</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1729,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121510346</v>
+        <v>121510250</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>100379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,46 +1746,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>705926</v>
+        <v>705934</v>
       </c>
       <c r="R11" t="n">
-        <v>6645152</v>
+        <v>6645213</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121510617</v>
+        <v>121510346</v>
       </c>
       <c r="B12" t="n">
-        <v>105218</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,41 +1848,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705913</v>
+        <v>705926</v>
       </c>
       <c r="R12" t="n">
-        <v>6645098</v>
+        <v>6645152</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121512264</v>
+        <v>121510395</v>
       </c>
       <c r="B13" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,38 +1955,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705936</v>
+        <v>705903</v>
       </c>
       <c r="R13" t="n">
-        <v>6645491</v>
+        <v>6645116</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2040,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121510646</v>
+        <v>121512264</v>
       </c>
       <c r="B14" t="n">
-        <v>105218</v>
+        <v>97067</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,21 +2066,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2080,10 +2090,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705903</v>
+        <v>705936</v>
       </c>
       <c r="R14" t="n">
-        <v>6645116</v>
+        <v>6645491</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,10 +2152,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121511629</v>
+        <v>121509872</v>
       </c>
       <c r="B15" t="n">
-        <v>100379</v>
+        <v>5173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,21 +2168,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,13 +2192,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705996</v>
+        <v>705878</v>
       </c>
       <c r="R15" t="n">
-        <v>6645057</v>
+        <v>6645330</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2244,10 +2254,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121510250</v>
+        <v>121510232</v>
       </c>
       <c r="B16" t="n">
-        <v>100379</v>
+        <v>90693</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,21 +2270,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2284,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705934</v>
+        <v>705933</v>
       </c>
       <c r="R16" t="n">
-        <v>6645213</v>
+        <v>6645178</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2356,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121510232</v>
+        <v>121510018</v>
       </c>
       <c r="B17" t="n">
         <v>90693</v>
@@ -2386,13 +2396,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705933</v>
+        <v>705808</v>
       </c>
       <c r="R17" t="n">
-        <v>6645178</v>
+        <v>6645334</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2448,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121510211</v>
+        <v>121511629</v>
       </c>
       <c r="B18" t="n">
-        <v>57373</v>
+        <v>100379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,43 +2470,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705870</v>
+        <v>705996</v>
       </c>
       <c r="R18" t="n">
-        <v>6645222</v>
+        <v>6645057</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2555,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121510395</v>
+        <v>121510646</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2567,33 +2572,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121509872</v>
+        <v>121510391</v>
       </c>
       <c r="B20" t="n">
-        <v>5173</v>
+        <v>100379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2678,21 +2678,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>705878</v>
+        <v>705926</v>
       </c>
       <c r="R20" t="n">
-        <v>6645330</v>
+        <v>6645152</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121511055</v>
+        <v>121510617</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>105218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,49 +1427,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>705844</v>
+        <v>705913</v>
       </c>
       <c r="R8" t="n">
-        <v>6645172</v>
+        <v>6645098</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1525,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121510617</v>
+        <v>121510395</v>
       </c>
       <c r="B9" t="n">
-        <v>105218</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,38 +1529,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>705913</v>
+        <v>705903</v>
       </c>
       <c r="R9" t="n">
-        <v>6645098</v>
+        <v>6645116</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1627,7 +1624,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121510211</v>
+        <v>121510346</v>
       </c>
       <c r="B10" t="n">
         <v>57373</v>
@@ -1672,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705870</v>
+        <v>705926</v>
       </c>
       <c r="R10" t="n">
-        <v>6645222</v>
+        <v>6645152</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1734,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121510250</v>
+        <v>121512264</v>
       </c>
       <c r="B11" t="n">
-        <v>100379</v>
+        <v>97067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,21 +1747,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1774,10 +1771,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>705934</v>
+        <v>705936</v>
       </c>
       <c r="R11" t="n">
-        <v>6645213</v>
+        <v>6645491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1836,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121510346</v>
+        <v>121511629</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>100379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,43 +1845,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705926</v>
+        <v>705996</v>
       </c>
       <c r="R12" t="n">
-        <v>6645152</v>
+        <v>6645057</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1943,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121510395</v>
+        <v>121510391</v>
       </c>
       <c r="B13" t="n">
-        <v>57373</v>
+        <v>100379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,46 +1947,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>705903</v>
+        <v>705926</v>
       </c>
       <c r="R13" t="n">
-        <v>6645116</v>
+        <v>6645152</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2050,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121512264</v>
+        <v>121509872</v>
       </c>
       <c r="B14" t="n">
-        <v>97067</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,21 +2053,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2090,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705936</v>
+        <v>705878</v>
       </c>
       <c r="R14" t="n">
-        <v>6645491</v>
+        <v>6645330</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121509872</v>
+        <v>121511055</v>
       </c>
       <c r="B15" t="n">
-        <v>5173</v>
+        <v>57373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,41 +2151,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>705878</v>
+        <v>705844</v>
       </c>
       <c r="R15" t="n">
-        <v>6645330</v>
+        <v>6645172</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2254,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121510232</v>
+        <v>121510211</v>
       </c>
       <c r="B16" t="n">
-        <v>90693</v>
+        <v>57373</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2266,41 +2261,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705933</v>
+        <v>705870</v>
       </c>
       <c r="R16" t="n">
-        <v>6645178</v>
+        <v>6645222</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121510018</v>
+        <v>121510232</v>
       </c>
       <c r="B17" t="n">
         <v>90693</v>
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705808</v>
+        <v>705933</v>
       </c>
       <c r="R17" t="n">
-        <v>6645334</v>
+        <v>6645178</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2458,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121511629</v>
+        <v>121510018</v>
       </c>
       <c r="B18" t="n">
-        <v>100379</v>
+        <v>90693</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2474,21 +2474,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705996</v>
+        <v>705808</v>
       </c>
       <c r="R18" t="n">
-        <v>6645057</v>
+        <v>6645334</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2662,7 +2662,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121510391</v>
+        <v>121510250</v>
       </c>
       <c r="B20" t="n">
         <v>100379</v>
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>705926</v>
+        <v>705934</v>
       </c>
       <c r="R20" t="n">
-        <v>6645152</v>
+        <v>6645213</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121510395</v>
+        <v>121511629</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>100379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,46 +1529,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>705903</v>
+        <v>705996</v>
       </c>
       <c r="R9" t="n">
-        <v>6645116</v>
+        <v>6645057</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1624,10 +1619,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121510346</v>
+        <v>121510232</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>90693</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,46 +1631,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>705926</v>
+        <v>705933</v>
       </c>
       <c r="R10" t="n">
-        <v>6645152</v>
+        <v>6645178</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1731,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121512264</v>
+        <v>121510646</v>
       </c>
       <c r="B11" t="n">
-        <v>97067</v>
+        <v>105218</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,21 +1737,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>705936</v>
+        <v>705903</v>
       </c>
       <c r="R11" t="n">
-        <v>6645491</v>
+        <v>6645116</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121511629</v>
+        <v>121509872</v>
       </c>
       <c r="B12" t="n">
-        <v>100379</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,21 +1839,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1873,13 +1863,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>705996</v>
+        <v>705878</v>
       </c>
       <c r="R12" t="n">
-        <v>6645057</v>
+        <v>6645330</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2037,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121509872</v>
+        <v>121510346</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,41 +2039,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>705878</v>
+        <v>705926</v>
       </c>
       <c r="R14" t="n">
-        <v>6645330</v>
+        <v>6645152</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2249,7 +2244,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121510211</v>
+        <v>121510395</v>
       </c>
       <c r="B16" t="n">
         <v>57373</v>
@@ -2294,13 +2289,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>705870</v>
+        <v>705903</v>
       </c>
       <c r="R16" t="n">
-        <v>6645222</v>
+        <v>6645116</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2356,7 +2351,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121510232</v>
+        <v>121510018</v>
       </c>
       <c r="B17" t="n">
         <v>90693</v>
@@ -2396,13 +2391,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705933</v>
+        <v>705808</v>
       </c>
       <c r="R17" t="n">
-        <v>6645178</v>
+        <v>6645334</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2458,10 +2453,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121510018</v>
+        <v>121510211</v>
       </c>
       <c r="B18" t="n">
-        <v>90693</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,38 +2465,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705808</v>
+        <v>705870</v>
       </c>
       <c r="R18" t="n">
-        <v>6645334</v>
+        <v>6645222</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121510646</v>
+        <v>121512264</v>
       </c>
       <c r="B19" t="n">
-        <v>105218</v>
+        <v>97067</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>705903</v>
+        <v>705936</v>
       </c>
       <c r="R19" t="n">
-        <v>6645116</v>
+        <v>6645491</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 56742-2024 artfynd.xlsx
+++ b/artfynd/A 56742-2024 artfynd.xlsx
@@ -2351,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121510018</v>
+        <v>121510211</v>
       </c>
       <c r="B17" t="n">
-        <v>90693</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,38 +2363,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>705808</v>
+        <v>705870</v>
       </c>
       <c r="R17" t="n">
-        <v>6645334</v>
+        <v>6645222</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2453,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121510211</v>
+        <v>121512264</v>
       </c>
       <c r="B18" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2465,46 +2470,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Norrn, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>705870</v>
+        <v>705936</v>
       </c>
       <c r="R18" t="n">
-        <v>6645222</v>
+        <v>6645491</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121512264</v>
+        <v>121510018</v>
       </c>
       <c r="B19" t="n">
-        <v>97067</v>
+        <v>90693</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,13 +2600,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>705936</v>
+        <v>705808</v>
       </c>
       <c r="R19" t="n">
-        <v>6645491</v>
+        <v>6645334</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
